--- a/tracking_forms/010_worker_timesheet_and_tracking_form--tracking_forms.xlsx
+++ b/tracking_forms/010_worker_timesheet_and_tracking_form--tracking_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>break_duration</t>
+          <t>break_duration_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Break Duration</t>
+          <t>Break Duration 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hours_worked</t>
+          <t>hours_worked_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hours Worked</t>
+          <t>Hours Worked 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>clock_out_time</t>
+          <t>clock_out_time_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Clock Out Time</t>
+          <t>Clock Out Time 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>total_hours_worked</t>
+          <t>total_hours_worked_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Total Hours Worked</t>
+          <t>Total Hours Worked 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>employee_name_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Employee Name 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
